--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julid\OneDrive\Documents\UiPath\rpa_001YahooFinanceReading\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87441897-2865-440D-B8FE-8CF0AA14A816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A51CF4C-3EFC-46C4-8CE2-60AEA762FD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11340" yWindow="5620" windowWidth="25580" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>Symbol,Symbol Url,Name,Column-2,Column-2 Url,Price,Change,Change %,Volume,Day Range,52 Wk Range</t>
+  </si>
+  <si>
+    <t>julidb710@gmail.com's workspace</t>
   </si>
 </sst>
 </file>
@@ -217,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -227,6 +230,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,7 +603,9 @@
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
